--- a/data/2026/10/pedidos_2026-10-23.xlsx
+++ b/data/2026/10/pedidos_2026-10-23.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0014532D"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BBF7D0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +64,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,154 +433,1335 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Nombre de contacto</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Telefono</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Municipio</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Direccion destinatario</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Punto de referencia</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Producto / Quien recibe</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Monto a cobrar (COD)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Ya pagado (Si=Estandar / No=COD)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Peso (Lbs)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Fecha de entrega</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Indicaciones para entrega</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Numero de emergencia</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Estado subida</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Error</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>discount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>observations</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>vat</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>type_id</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>apellido</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>apellido2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>apellido_destino</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>lugar_nacimiento</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1. Hugo Ernesto Calderón Peraza</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Hugo Ernesto Calderón Peraza</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>70647282</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Colonia Sitio del Niño, 7.ª Calle, Casa #13</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>en el desvío de Opico</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>La Libertad</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>SAN JUAN OPICO</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Colonia Sitio del Niño, 7.ª Calle, Casa #13</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>en el desvío de Opico</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>2x1 Aviador Dorado y Aviador Negro</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Contactar al cliente para coordinar la entrega</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>José Roberto Andaluz Quezada</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>76153766</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Residencial Bella Granada</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>casa 13 B | 13.823474, -89.270482</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>La Libertad</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>QUEZALTEPEQUE</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Casio square plata con negro</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>María Vicenta Ruiz</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>72889754</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Comedor El Taurete, San Francisco Javier, Usulután</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Frente a Telecom | 13.419305, -88.571336</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Usulután</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SAN FRANCISCO JAVIER</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Retro Black</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>David Alexander Martinez</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>76087888</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bulevar del Ejército Nacional, Km 7 ½</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>frente a Leche Salud | 3.696046, -89.133937</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>San Salvador</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SOYAPANGO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Rose gold Diamond + Regalía wood negro</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jorge Alberto Peraza</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>70248494</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Playa San Diego</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Centro Escolar Playa San Diego | 13.469911, -89.257444</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>La Libertad</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Rose gold Mini</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>José Edgar Menjivar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>74303372</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Barrio San Antonio Colonia Zacamil</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>frente a Hiper Paca. | 14.039544, -88.933818</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chalatenango</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CHALATENANGO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Casio World</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Emiliana Castro</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>76132041</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Colonia 5 Cedros, Lourdes Colón, La Libertad.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Punto de referencia: Nuevo deportivo de 5 Cedros sobre la novena. | 13.730836, -89.379985</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>La Libertad</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>COLON</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Rose gold Mini</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>David Gómez</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>76016534</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>La Unión centro, Comedor Golden Coral,</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>a la par de Little César, Recibe Sarita Reyes | 13.337543, -87.844993</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>LA UNION</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Casio cuero MTPV002GL fondo negro con dorado y correa cafe</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Obed isai torres amaya</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>79194511</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TEXACO • San Miguel</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>junto a walmart | 13.451896, -88.158789</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Casio old money rose gold</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Juan Francisco Pineda</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>75406525</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Calle Morazán #43 Bo. El Calvario</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Farmacia El Calvario, lugar de trabajo | 14.043117, -88.935644</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chalatenango</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CHALATENANGO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Casio old money rose gold</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Karen Beatriz Peñate Trujillo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>76856904</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pasaje barrera, una cuadra antes del liceo El Salvador,</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>casa doble planta de esquina | 13.979880, -89.682114</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CHALCHUAPA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Casio old money milano negro</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Lorena Gricelda Aguilar Orellana</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>77362093</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mercado Plazuela Colón</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>13 calle, local #33, Santa Ana | 13.988848, -89.563206</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Casio old money rose gold</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Noemi</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>75739155</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Entrega en parque central de Quezaltepeque, La Libertad</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Parque central | 13.831237, -89.272268</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>La Libertad</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>QUEZALTEPEQUE</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Casio retro rose gold</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Estefany Elizabeth Serrano De León</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>70330114</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Col la hermita 1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>calle fray Martín de Porres casa g8 | 13.809230, -89.175857</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>San Salvador</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>APOPA</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Casio world plata mas regalia</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stefany</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>75918751</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Colonia Vista Hermosa</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>por la caseta policial en San Francisco Gotera Morazán | 13.695803, -88.105222</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Morazán</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SAN FRANCISCO GOTERA</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Casio retro rose gold</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>pagado cambio, cliente entrega producto</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Samuel Díaz</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>68590103</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Colonia 15 de septiembre</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>avenida La Paz | 13.481582, -88.159401</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Casio heritage verde oscuro</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Karla Marcela Romualdo Mendoza</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>70001351</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ecoterra Maquilishuat</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>polígono 14 casa 2 | 13.991062, -89.609090</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SANTA ANA</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Casio rose gold mini + Casio Old Money Rose gold</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Morales</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>72742306</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>colonia arcos de san francisco</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>referencia: Casa número 1 frente ala pluma | 13.476636, -88.161904</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>casio f105</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Edgar Moran</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>70232177</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Calle Ppal Entre San Jose Y Santa Marina</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Iglesia de Dios Colonias Unidas San José | 13.968430,-89.547292</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>SANTA ANA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Casio heritage plata</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ricardo Antonio Velásquez Carrillo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>78972097</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Barrio el Calvario 6a Calle poniente Casa #4 Cojutepeque, Cuscatlan.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Punto de referencia: de la tienda de camisetas de fútbol y ropa deportiva, media cuadra hacia dentro. Casa con muro color naranja | 13.723052, -88.941249</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cuscatlán</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>COJUTEPEQUE</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Seiko 5 fondo azul</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
